--- a/data/TemporalNMR_plant.xlsx
+++ b/data/TemporalNMR_plant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/arjun_chakrawal_pnnl_gov/Documents/MONet/DynamicDRmodel/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/arjun_chakrawal_pnnl_gov/Documents/MONet/DynamicDRmodel/chemodiv-litter-model/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="690" documentId="11_07F15861874AF80F62355476585DCE3A8756860C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A1AB25C-B1F9-4780-A1EB-9F7A3CB973BC}"/>
+  <xr:revisionPtr revIDLastSave="735" documentId="11_07F15861874AF80F62355476585DCE3A8756860C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43394D65-ADCC-48D7-865E-568257892884}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="551" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,17 +46,6 @@
     <author>tc={F5A32AE6-E37D-4729-A54D-A94870919EAF}</author>
     <author>tc={18B023DE-6BF1-43E6-BAF1-3F343FF0B91D}</author>
     <author>tc={AB22B0EF-AF0D-4F88-BBAF-A1BFB3567315}</author>
-    <author>tc={10DEDF6D-70DB-4772-BC91-9BCE7A1402DD}</author>
-    <author>tc={8A8E0B82-DE89-4FA3-A09C-172CFE7D13E3}</author>
-    <author>tc={7655C9A3-B06C-469E-9DC5-79A16927E9AC}</author>
-    <author>tc={61505BF3-18DA-4ACF-9C2D-5706ED4D6C05}</author>
-    <author>tc={0FDF1883-619C-4D17-893C-8FA6AD44F782}</author>
-    <author>tc={B52756ED-E732-4879-A993-780830B4D9D3}</author>
-    <author>tc={9261AF63-284A-4C68-A262-B2B7B5D6BA2D}</author>
-    <author>tc={E35AB951-EA3E-4CD4-8986-8B20202B6978}</author>
-    <author>tc={438FB0DE-5303-4C8D-8077-345A6BB32FB6}</author>
-    <author>tc={1886D323-DA12-49B6-8917-C7EC1135AA5C}</author>
-    <author>tc={DE339B0F-1D0B-4223-9CCC-316188C4AD42}</author>
     <author>tc={F467A315-8850-4036-82DC-B963C75E5EB7}</author>
     <author>tc={9F1702AA-CFA5-4F2D-9BA1-F6EC5FEFF97C}</author>
     <author>tc={F6FED9C7-33D0-4D45-9400-E8E6D2F9D610}</author>
@@ -129,95 +118,7 @@
     Values read from Figure 1 https://doi.org/10.1080/00103620600767108</t>
       </text>
     </comment>
-    <comment ref="M152" authorId="8" shapeId="0" xr:uid="{10DEDF6D-70DB-4772-BC91-9BCE7A1402DD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M157" authorId="9" shapeId="0" xr:uid="{8A8E0B82-DE89-4FA3-A09C-172CFE7D13E3}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M162" authorId="10" shapeId="0" xr:uid="{7655C9A3-B06C-469E-9DC5-79A16927E9AC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M166" authorId="11" shapeId="0" xr:uid="{61505BF3-18DA-4ACF-9C2D-5706ED4D6C05}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M170" authorId="12" shapeId="0" xr:uid="{0FDF1883-619C-4D17-893C-8FA6AD44F782}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M174" authorId="13" shapeId="0" xr:uid="{B52756ED-E732-4879-A993-780830B4D9D3}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M178" authorId="14" shapeId="0" xr:uid="{9261AF63-284A-4C68-A262-B2B7B5D6BA2D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M182" authorId="15" shapeId="0" xr:uid="{E35AB951-EA3E-4CD4-8986-8B20202B6978}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M186" authorId="16" shapeId="0" xr:uid="{438FB0DE-5303-4C8D-8077-345A6BB32FB6}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M190" authorId="17" shapeId="0" xr:uid="{1886D323-DA12-49B6-8917-C7EC1135AA5C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M194" authorId="18" shapeId="0" xr:uid="{DE339B0F-1D0B-4223-9CCC-316188C4AD42}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</t>
-      </text>
-    </comment>
-    <comment ref="M204" authorId="19" shapeId="0" xr:uid="{F467A315-8850-4036-82DC-B963C75E5EB7}">
+    <comment ref="M204" authorId="8" shapeId="0" xr:uid="{F467A315-8850-4036-82DC-B963C75E5EB7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -225,7 +126,7 @@
     Supplementary of Pastorelli</t>
       </text>
     </comment>
-    <comment ref="N221" authorId="20" shapeId="0" xr:uid="{9F1702AA-CFA5-4F2D-9BA1-F6EC5FEFF97C}">
+    <comment ref="N221" authorId="9" shapeId="0" xr:uid="{9F1702AA-CFA5-4F2D-9BA1-F6EC5FEFF97C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -233,7 +134,7 @@
     Source: https://en.climate-data.org/europe/italy/campania-432/</t>
       </text>
     </comment>
-    <comment ref="M379" authorId="21" shapeId="0" xr:uid="{F6FED9C7-33D0-4D45-9400-E8E6D2F9D610}">
+    <comment ref="M379" authorId="10" shapeId="0" xr:uid="{F6FED9C7-33D0-4D45-9400-E8E6D2F9D610}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1501,105 +1402,6 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="M152" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{10DEDF6D-70DB-4772-BC91-9BCE7A1402DD}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M157" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{8A8E0B82-DE89-4FA3-A09C-172CFE7D13E3}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M162" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{7655C9A3-B06C-469E-9DC5-79A16927E9AC}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M166" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{61505BF3-18DA-4ACF-9C2D-5706ED4D6C05}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M170" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{0FDF1883-619C-4D17-893C-8FA6AD44F782}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M174" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{B52756ED-E732-4879-A993-780830B4D9D3}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M178" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{9261AF63-284A-4C68-A262-B2B7B5D6BA2D}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M182" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{E35AB951-EA3E-4CD4-8986-8B20202B6978}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M186" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{438FB0DE-5303-4C8D-8077-345A6BB32FB6}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M190" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{1886D323-DA12-49B6-8917-C7EC1135AA5C}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="M194" dT="2024-04-14T03:45:34.84" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{DE339B0F-1D0B-4223-9CCC-316188C4AD42}">
-    <text>Monthly average taken from  table 2.2 https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3432625193</xltc2:checksum>
-        <xltc2:hyperlink startIndex="38" length="61" url="https://link.springer.com/chapter/10.1007/978-4-431-67879-3_2"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
   <threadedComment ref="M204" dT="2024-04-14T05:14:09.52" personId="{2278B182-5FEE-4CEB-A933-04BF943E7B0B}" id="{F467A315-8850-4036-82DC-B963C75E5EB7}">
     <text>Supplementary of Pastorelli</text>
   </threadedComment>
@@ -1626,22 +1428,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BZ390"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
-    <col min="5" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="1" customWidth="1"/>
-    <col min="13" max="15" width="9.140625" style="1"/>
+    <col min="5" max="7" width="9.140625" style="1"/>
+    <col min="8" max="9" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="21" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="15" width="9.140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="3" style="1" customWidth="1"/>
-    <col min="17" max="18" width="9.140625" style="1"/>
+    <col min="17" max="18" width="9.140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.140625" style="1" customWidth="1"/>
     <col min="21" max="45" width="9.140625" style="1"/>
     <col min="46" max="46" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1786,7 +1587,7 @@
       </c>
       <c r="AU1" s="3"/>
     </row>
-    <row r="2" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2009</v>
       </c>
@@ -1917,7 +1718,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2009</v>
       </c>
@@ -2048,7 +1849,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2009</v>
       </c>
@@ -2179,7 +1980,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2009</v>
       </c>
@@ -2310,7 +2111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2009</v>
       </c>
@@ -2441,7 +2242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2009</v>
       </c>
@@ -2572,7 +2373,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2009</v>
       </c>
@@ -2703,7 +2504,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2009</v>
       </c>
@@ -2834,7 +2635,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2009</v>
       </c>
@@ -2965,7 +2766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -3096,7 +2897,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2009</v>
       </c>
@@ -3227,7 +3028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2009</v>
       </c>
@@ -3340,7 +3141,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2009</v>
       </c>
@@ -3465,7 +3266,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2009</v>
       </c>
@@ -3590,7 +3391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2009</v>
       </c>
@@ -3715,7 +3516,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2009</v>
       </c>
@@ -3840,7 +3641,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2009</v>
       </c>
@@ -3965,7 +3766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2009</v>
       </c>
@@ -4090,7 +3891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2009</v>
       </c>
@@ -4215,7 +4016,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -4340,7 +4141,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2009</v>
       </c>
@@ -4465,7 +4266,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2009</v>
       </c>
@@ -4590,7 +4391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2009</v>
       </c>
@@ -4709,7 +4510,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2009</v>
       </c>
@@ -4840,7 +4641,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2009</v>
       </c>
@@ -4959,7 +4760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>2009</v>
       </c>
@@ -5078,7 +4879,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>2009</v>
       </c>
@@ -5209,7 +5010,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>2009</v>
       </c>
@@ -5328,7 +5129,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2009</v>
       </c>
@@ -5447,7 +5248,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2009</v>
       </c>
@@ -5566,7 +5367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>2009</v>
       </c>
@@ -5685,7 +5486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>2009</v>
       </c>
@@ -5804,7 +5605,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2009</v>
       </c>
@@ -5935,7 +5736,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2000</v>
       </c>
@@ -6048,7 +5849,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>2000</v>
       </c>
@@ -6161,7 +5962,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>2000</v>
       </c>
@@ -6274,7 +6075,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>2000</v>
       </c>
@@ -6387,7 +6188,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>2000</v>
       </c>
@@ -6500,7 +6301,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2000</v>
       </c>
@@ -6613,7 +6414,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2000</v>
       </c>
@@ -6726,7 +6527,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>2000</v>
       </c>
@@ -6839,7 +6640,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>2000</v>
       </c>
@@ -6952,7 +6753,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>2000</v>
       </c>
@@ -7065,7 +6866,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>2000</v>
       </c>
@@ -7178,7 +6979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>2000</v>
       </c>
@@ -7291,7 +7092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>2000</v>
       </c>
@@ -7404,7 +7205,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>2000</v>
       </c>
@@ -7517,7 +7318,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>2000</v>
       </c>
@@ -7630,7 +7431,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>2000</v>
       </c>
@@ -7743,7 +7544,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>2000</v>
       </c>
@@ -7856,7 +7657,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>2000</v>
       </c>
@@ -7969,7 +7770,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>2000</v>
       </c>
@@ -8082,7 +7883,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>2000</v>
       </c>
@@ -8195,7 +7996,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2000</v>
       </c>
@@ -8308,7 +8109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>2000</v>
       </c>
@@ -8421,7 +8222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>2000</v>
       </c>
@@ -8534,7 +8335,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>2000</v>
       </c>
@@ -8647,7 +8448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>2000</v>
       </c>
@@ -8760,7 +8561,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>2000</v>
       </c>
@@ -8873,7 +8674,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>2000</v>
       </c>
@@ -8986,7 +8787,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="62" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>2000</v>
       </c>
@@ -9099,7 +8900,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>2000</v>
       </c>
@@ -9212,7 +9013,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>2000</v>
       </c>
@@ -9325,7 +9126,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>2000</v>
       </c>
@@ -9438,7 +9239,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>2000</v>
       </c>
@@ -9551,7 +9352,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>2000</v>
       </c>
@@ -9664,7 +9465,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>2000</v>
       </c>
@@ -9777,7 +9578,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>2000</v>
       </c>
@@ -9890,7 +9691,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>2000</v>
       </c>
@@ -10003,7 +9804,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>2017</v>
       </c>
@@ -10113,7 +9914,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>2017</v>
       </c>
@@ -10223,7 +10024,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>2017</v>
       </c>
@@ -10333,7 +10134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>2017</v>
       </c>
@@ -10443,7 +10244,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>2017</v>
       </c>
@@ -10553,7 +10354,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>2017</v>
       </c>
@@ -10663,7 +10464,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="77" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>2017</v>
       </c>
@@ -10773,7 +10574,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>2017</v>
       </c>
@@ -10883,7 +10684,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>2017</v>
       </c>
@@ -10993,7 +10794,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>2017</v>
       </c>
@@ -11103,7 +10904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>2017</v>
       </c>
@@ -11213,7 +11014,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>2017</v>
       </c>
@@ -11323,7 +11124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>2017</v>
       </c>
@@ -11433,7 +11234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>2017</v>
       </c>
@@ -11543,7 +11344,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>2017</v>
       </c>
@@ -11653,7 +11454,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>2005</v>
       </c>
@@ -11776,7 +11577,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="87" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>2005</v>
       </c>
@@ -11859,7 +11660,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="88" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>2005</v>
       </c>
@@ -11942,7 +11743,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="89" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>2005</v>
       </c>
@@ -12025,7 +11826,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="90" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>2005</v>
       </c>
@@ -12108,7 +11909,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="91" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>2005</v>
       </c>
@@ -12191,7 +11992,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="92" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>2005</v>
       </c>
@@ -12313,7 +12114,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>2005</v>
       </c>
@@ -12435,7 +12236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>2005</v>
       </c>
@@ -12558,7 +12359,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>2005</v>
       </c>
@@ -12641,7 +12442,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="96" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>2005</v>
       </c>
@@ -12724,7 +12525,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="97" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>2005</v>
       </c>
@@ -12807,7 +12608,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="98" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>2005</v>
       </c>
@@ -12890,7 +12691,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="99" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>2005</v>
       </c>
@@ -12973,7 +12774,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="100" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>2005</v>
       </c>
@@ -13095,7 +12896,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>2005</v>
       </c>
@@ -13217,7 +13018,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="102" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>2005</v>
       </c>
@@ -13340,7 +13141,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="103" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>2005</v>
       </c>
@@ -13423,7 +13224,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="104" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>2005</v>
       </c>
@@ -13506,7 +13307,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="105" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>2005</v>
       </c>
@@ -13589,7 +13390,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="106" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>2005</v>
       </c>
@@ -13672,7 +13473,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="107" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>2005</v>
       </c>
@@ -13755,7 +13556,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="108" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>2005</v>
       </c>
@@ -13877,7 +13678,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="109" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>2005</v>
       </c>
@@ -13999,7 +13800,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>2004</v>
       </c>
@@ -14115,7 +13916,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="111" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>2004</v>
       </c>
@@ -14231,7 +14032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="112" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>2004</v>
       </c>
@@ -14342,7 +14143,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>2004</v>
       </c>
@@ -14453,7 +14254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>2004</v>
       </c>
@@ -14567,7 +14368,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>2004</v>
       </c>
@@ -14681,7 +14482,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="116" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>2007</v>
       </c>
@@ -14797,7 +14598,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="117" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>2007</v>
       </c>
@@ -14905,7 +14706,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="118" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>2007</v>
       </c>
@@ -15013,7 +14814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="119" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>2007</v>
       </c>
@@ -15121,7 +14922,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="120" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>2007</v>
       </c>
@@ -15237,7 +15038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>2007</v>
       </c>
@@ -15345,7 +15146,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="122" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>2007</v>
       </c>
@@ -15453,7 +15254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="123" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>2007</v>
       </c>
@@ -15561,7 +15362,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="124" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>2007</v>
       </c>
@@ -15677,7 +15478,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="125" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>2007</v>
       </c>
@@ -15785,7 +15586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="126" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>2007</v>
       </c>
@@ -15893,7 +15694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="127" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>2007</v>
       </c>
@@ -16001,7 +15802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="128" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>2007</v>
       </c>
@@ -16117,7 +15918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="129" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>2007</v>
       </c>
@@ -16225,7 +16026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="130" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>2007</v>
       </c>
@@ -16333,7 +16134,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>2007</v>
       </c>
@@ -16441,7 +16242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="132" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>2007</v>
       </c>
@@ -16557,7 +16358,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="133" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>2007</v>
       </c>
@@ -16665,7 +16466,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="134" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>2007</v>
       </c>
@@ -16773,7 +16574,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>2007</v>
       </c>
@@ -16881,7 +16682,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="136" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>2007</v>
       </c>
@@ -16973,7 +16774,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="137" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>2007</v>
       </c>
@@ -17081,7 +16882,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="138" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>2007</v>
       </c>
@@ -17189,7 +16990,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="139" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>2007</v>
       </c>
@@ -17297,7 +17098,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="140" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>2007</v>
       </c>
@@ -17413,7 +17214,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="141" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>2007</v>
       </c>
@@ -17521,7 +17322,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>2007</v>
       </c>
@@ -17629,7 +17430,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>2007</v>
       </c>
@@ -17737,7 +17538,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="144" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>2007</v>
       </c>
@@ -17853,7 +17654,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="145" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>2007</v>
       </c>
@@ -17961,7 +17762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="146" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>2007</v>
       </c>
@@ -18069,7 +17870,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="147" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>2007</v>
       </c>
@@ -18177,7 +17978,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="148" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>2007</v>
       </c>
@@ -18293,7 +18094,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>2007</v>
       </c>
@@ -18401,7 +18202,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="150" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>2007</v>
       </c>
@@ -18509,7 +18310,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="151" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>2007</v>
       </c>
@@ -18617,7 +18418,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>2009</v>
       </c>
@@ -18655,10 +18456,10 @@
         <v>8.9</v>
       </c>
       <c r="N152" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O152" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P152" s="1">
         <v>0</v>
@@ -18718,7 +18519,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="153" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>2009</v>
       </c>
@@ -18757,10 +18558,10 @@
         <v>15.4</v>
       </c>
       <c r="N153" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O153" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P153" s="1">
         <v>0</v>
@@ -18793,7 +18594,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="154" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>2009</v>
       </c>
@@ -18832,10 +18633,10 @@
         <v>8.9</v>
       </c>
       <c r="N154" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O154" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P154" s="1">
         <v>0</v>
@@ -18895,7 +18696,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="155" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>2009</v>
       </c>
@@ -18934,10 +18735,10 @@
         <v>8.9</v>
       </c>
       <c r="N155" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O155" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P155" s="1">
         <v>0</v>
@@ -18997,7 +18798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="156" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>2009</v>
       </c>
@@ -19036,10 +18837,10 @@
         <v>8.9</v>
       </c>
       <c r="N156" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O156" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P156" s="1">
         <v>0</v>
@@ -19099,7 +18900,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="157" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>2009</v>
       </c>
@@ -19137,10 +18938,10 @@
         <v>8.9</v>
       </c>
       <c r="N157" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O157" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P157" s="1">
         <v>0</v>
@@ -19200,7 +19001,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="158" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>2009</v>
       </c>
@@ -19239,10 +19040,10 @@
         <v>15.4</v>
       </c>
       <c r="N158" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O158" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P158" s="1">
         <v>0</v>
@@ -19275,7 +19076,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="159" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>2009</v>
       </c>
@@ -19314,10 +19115,10 @@
         <v>8.9</v>
       </c>
       <c r="N159" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O159" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P159" s="1">
         <v>0</v>
@@ -19377,7 +19178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="160" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>2009</v>
       </c>
@@ -19416,10 +19217,10 @@
         <v>8.9</v>
       </c>
       <c r="N160" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O160" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P160" s="1">
         <v>0</v>
@@ -19479,7 +19280,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="161" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>2009</v>
       </c>
@@ -19518,10 +19319,10 @@
         <v>8.9</v>
       </c>
       <c r="N161" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O161" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="P161" s="1">
         <v>0</v>
@@ -19581,7 +19382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="162" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>2011</v>
       </c>
@@ -19619,10 +19420,10 @@
         <v>8.9</v>
       </c>
       <c r="N162" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O162" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q162" s="1" t="s">
         <v>58</v>
@@ -19679,7 +19480,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>2011</v>
       </c>
@@ -19718,10 +19519,10 @@
         <v>15.4</v>
       </c>
       <c r="N163" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O163" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q163" s="1" t="s">
         <v>58</v>
@@ -19778,7 +19579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="164" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>2011</v>
       </c>
@@ -19817,10 +19618,10 @@
         <v>8.9</v>
       </c>
       <c r="N164" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O164" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q164" s="1" t="s">
         <v>58</v>
@@ -19877,7 +19678,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="165" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>2011</v>
       </c>
@@ -19916,10 +19717,10 @@
         <v>8.9</v>
       </c>
       <c r="N165" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O165" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q165" s="1" t="s">
         <v>58</v>
@@ -19976,7 +19777,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="166" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>2011</v>
       </c>
@@ -20014,10 +19815,10 @@
         <v>8.9</v>
       </c>
       <c r="N166" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O166" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q166" s="1" t="s">
         <v>58</v>
@@ -20074,7 +19875,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>2011</v>
       </c>
@@ -20113,10 +19914,10 @@
         <v>15.4</v>
       </c>
       <c r="N167" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O167" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q167" s="1" t="s">
         <v>58</v>
@@ -20173,7 +19974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="168" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>2011</v>
       </c>
@@ -20212,10 +20013,10 @@
         <v>8.9</v>
       </c>
       <c r="N168" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O168" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q168" s="1" t="s">
         <v>58</v>
@@ -20272,7 +20073,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>2011</v>
       </c>
@@ -20311,10 +20112,10 @@
         <v>8.9</v>
       </c>
       <c r="N169" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O169" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q169" s="1" t="s">
         <v>58</v>
@@ -20371,7 +20172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="170" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>2013</v>
       </c>
@@ -20409,10 +20210,10 @@
         <v>8.9</v>
       </c>
       <c r="N170" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O170" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q170" s="1" t="s">
         <v>58</v>
@@ -20460,7 +20261,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="171" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>2013</v>
       </c>
@@ -20499,10 +20300,10 @@
         <v>15.4</v>
       </c>
       <c r="N171" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O171" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q171" s="1" t="s">
         <v>58</v>
@@ -20550,7 +20351,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="172" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>2013</v>
       </c>
@@ -20589,10 +20390,10 @@
         <v>8.9</v>
       </c>
       <c r="N172" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O172" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q172" s="1" t="s">
         <v>58</v>
@@ -20640,7 +20441,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="173" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>2013</v>
       </c>
@@ -20679,10 +20480,10 @@
         <v>8.9</v>
       </c>
       <c r="N173" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O173" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q173" s="1" t="s">
         <v>58</v>
@@ -20730,7 +20531,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="174" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>2013</v>
       </c>
@@ -20768,10 +20569,10 @@
         <v>8.9</v>
       </c>
       <c r="N174" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O174" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q174" s="1" t="s">
         <v>58</v>
@@ -20819,7 +20620,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="175" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>2013</v>
       </c>
@@ -20858,10 +20659,10 @@
         <v>15.4</v>
       </c>
       <c r="N175" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O175" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q175" s="1" t="s">
         <v>58</v>
@@ -20909,7 +20710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="176" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>2013</v>
       </c>
@@ -20948,10 +20749,10 @@
         <v>8.9</v>
       </c>
       <c r="N176" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O176" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q176" s="1" t="s">
         <v>58</v>
@@ -20999,7 +20800,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="177" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>2013</v>
       </c>
@@ -21038,10 +20839,10 @@
         <v>8.9</v>
       </c>
       <c r="N177" s="1">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="O177" s="1">
-        <v>516</v>
+        <v>1111</v>
       </c>
       <c r="Q177" s="1" t="s">
         <v>58</v>
@@ -21089,7 +20890,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="178" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>2013</v>
       </c>
@@ -21127,10 +20928,10 @@
         <v>8.9</v>
       </c>
       <c r="N178" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O178" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q178" s="1" t="s">
         <v>58</v>
@@ -21150,6 +20951,15 @@
       <c r="W178" s="1">
         <v>100</v>
       </c>
+      <c r="X178" s="1">
+        <v>516.20000000000005</v>
+      </c>
+      <c r="Y178" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="Z178" s="1">
+        <v>46.1</v>
+      </c>
       <c r="AE178" s="1">
         <v>0.19800000000000001</v>
       </c>
@@ -21178,7 +20988,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="179" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>2013</v>
       </c>
@@ -21217,10 +21027,10 @@
         <v>15.4</v>
       </c>
       <c r="N179" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O179" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q179" s="1" t="s">
         <v>58</v>
@@ -21240,6 +21050,15 @@
       <c r="W179" s="1">
         <v>76.099999999999994</v>
       </c>
+      <c r="X179" s="1">
+        <v>505</v>
+      </c>
+      <c r="Y179" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="Z179" s="1">
+        <v>26.4</v>
+      </c>
       <c r="AE179" s="1">
         <v>0.22500000000000001</v>
       </c>
@@ -21268,7 +21087,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="180" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>2013</v>
       </c>
@@ -21307,10 +21126,10 @@
         <v>8.9</v>
       </c>
       <c r="N180" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O180" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q180" s="1" t="s">
         <v>58</v>
@@ -21330,6 +21149,15 @@
       <c r="W180" s="1">
         <v>49.3</v>
       </c>
+      <c r="X180" s="1">
+        <v>465.9</v>
+      </c>
+      <c r="Y180" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="Z180" s="1">
+        <v>21.9</v>
+      </c>
       <c r="AE180" s="1">
         <v>0.24199999999999999</v>
       </c>
@@ -21358,7 +21186,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="181" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>2013</v>
       </c>
@@ -21397,10 +21225,10 @@
         <v>8.9</v>
       </c>
       <c r="N181" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O181" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q181" s="1" t="s">
         <v>58</v>
@@ -21420,6 +21248,15 @@
       <c r="W181" s="1">
         <v>32.700000000000003</v>
       </c>
+      <c r="X181" s="1">
+        <v>458.8</v>
+      </c>
+      <c r="Y181" s="1">
+        <v>22.9</v>
+      </c>
+      <c r="Z181" s="1">
+        <v>20</v>
+      </c>
       <c r="AE181" s="1">
         <v>0.25600000000000001</v>
       </c>
@@ -21448,7 +21285,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="182" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>2013</v>
       </c>
@@ -21486,10 +21323,10 @@
         <v>8.9</v>
       </c>
       <c r="N182" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O182" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q182" s="1" t="s">
         <v>58</v>
@@ -21509,6 +21346,15 @@
       <c r="W182" s="1">
         <v>100</v>
       </c>
+      <c r="X182" s="1">
+        <v>522.79999999999995</v>
+      </c>
+      <c r="Y182" s="1">
+        <v>11.6</v>
+      </c>
+      <c r="Z182" s="1">
+        <v>45.1</v>
+      </c>
       <c r="AE182" s="1">
         <v>0.222</v>
       </c>
@@ -21537,7 +21383,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="183" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>2013</v>
       </c>
@@ -21576,10 +21422,10 @@
         <v>15.4</v>
       </c>
       <c r="N183" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O183" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q183" s="1" t="s">
         <v>58</v>
@@ -21599,6 +21445,15 @@
       <c r="W183" s="1">
         <v>70</v>
       </c>
+      <c r="X183" s="1">
+        <v>524.4</v>
+      </c>
+      <c r="Y183" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="Z183" s="1">
+        <v>28.2</v>
+      </c>
       <c r="AE183" s="1">
         <v>0.22500000000000001</v>
       </c>
@@ -21627,7 +21482,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>2013</v>
       </c>
@@ -21666,10 +21521,10 @@
         <v>8.9</v>
       </c>
       <c r="N184" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O184" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q184" s="1" t="s">
         <v>58</v>
@@ -21689,6 +21544,15 @@
       <c r="W184" s="1">
         <v>42.8</v>
       </c>
+      <c r="X184" s="1">
+        <v>500.3</v>
+      </c>
+      <c r="Y184" s="1">
+        <v>22.6</v>
+      </c>
+      <c r="Z184" s="1">
+        <v>22.2</v>
+      </c>
       <c r="AE184" s="1">
         <v>0.23899999999999999</v>
       </c>
@@ -21717,7 +21581,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="185" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>2013</v>
       </c>
@@ -21756,10 +21620,10 @@
         <v>8.9</v>
       </c>
       <c r="N185" s="1">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="O185" s="1">
-        <v>516</v>
+        <v>2031</v>
       </c>
       <c r="Q185" s="1" t="s">
         <v>58</v>
@@ -21779,6 +21643,15 @@
       <c r="W185" s="1">
         <v>26.9</v>
       </c>
+      <c r="X185" s="1">
+        <v>416.8</v>
+      </c>
+      <c r="Y185" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="Z185" s="1">
+        <v>18.8</v>
+      </c>
       <c r="AE185" s="1">
         <v>0.26600000000000001</v>
       </c>
@@ -21807,7 +21680,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="186" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>2013</v>
       </c>
@@ -21845,10 +21718,10 @@
         <v>8.9</v>
       </c>
       <c r="N186" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O186" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q186" s="1" t="s">
         <v>58</v>
@@ -21868,6 +21741,15 @@
       <c r="W186" s="1">
         <v>100</v>
       </c>
+      <c r="X186" s="1">
+        <v>609.4</v>
+      </c>
+      <c r="Y186" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="Z186" s="1">
+        <v>57.4</v>
+      </c>
       <c r="AE186" s="1">
         <v>0.28100000000000003</v>
       </c>
@@ -21896,7 +21778,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="187" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>2013</v>
       </c>
@@ -21935,10 +21817,10 @@
         <v>15.4</v>
       </c>
       <c r="N187" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O187" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q187" s="1" t="s">
         <v>58</v>
@@ -21958,6 +21840,15 @@
       <c r="W187" s="1">
         <v>48.1</v>
       </c>
+      <c r="X187" s="1">
+        <v>576.79999999999995</v>
+      </c>
+      <c r="Y187" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="Z187" s="1">
+        <v>34.6</v>
+      </c>
       <c r="AE187" s="1">
         <v>0.313</v>
       </c>
@@ -21986,7 +21877,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="188" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>2013</v>
       </c>
@@ -22025,10 +21916,10 @@
         <v>8.9</v>
       </c>
       <c r="N188" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O188" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q188" s="1" t="s">
         <v>58</v>
@@ -22048,6 +21939,15 @@
       <c r="W188" s="1">
         <v>41.9</v>
       </c>
+      <c r="X188" s="1">
+        <v>572.1</v>
+      </c>
+      <c r="Y188" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="Z188" s="1">
+        <v>29.1</v>
+      </c>
       <c r="AE188" s="1">
         <v>0.25600000000000001</v>
       </c>
@@ -22076,7 +21976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="189" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>2013</v>
       </c>
@@ -22115,10 +22015,10 @@
         <v>8.9</v>
       </c>
       <c r="N189" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O189" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q189" s="1" t="s">
         <v>58</v>
@@ -22138,6 +22038,15 @@
       <c r="W189" s="1">
         <v>33.799999999999997</v>
       </c>
+      <c r="X189" s="1">
+        <v>559.4</v>
+      </c>
+      <c r="Y189" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="Z189" s="1">
+        <v>25.7</v>
+      </c>
       <c r="AE189" s="1">
         <v>0.254</v>
       </c>
@@ -22166,7 +22075,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="190" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>2013</v>
       </c>
@@ -22204,10 +22113,10 @@
         <v>8.9</v>
       </c>
       <c r="N190" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O190" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q190" s="1" t="s">
         <v>58</v>
@@ -22227,6 +22136,15 @@
       <c r="W190" s="1">
         <v>100</v>
       </c>
+      <c r="X190" s="1">
+        <v>592.70000000000005</v>
+      </c>
+      <c r="Y190" s="1">
+        <v>11.1</v>
+      </c>
+      <c r="Z190" s="1">
+        <v>53.2</v>
+      </c>
       <c r="AE190" s="1">
         <v>0.28599999999999998</v>
       </c>
@@ -22255,7 +22173,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>2013</v>
       </c>
@@ -22294,10 +22212,10 @@
         <v>15.4</v>
       </c>
       <c r="N191" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O191" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q191" s="1" t="s">
         <v>58</v>
@@ -22317,6 +22235,15 @@
       <c r="W191" s="1">
         <v>59.3</v>
       </c>
+      <c r="X191" s="1">
+        <v>569.20000000000005</v>
+      </c>
+      <c r="Y191" s="1">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="Z191" s="1">
+        <v>28.5</v>
+      </c>
       <c r="AE191" s="1">
         <v>0.29199999999999998</v>
       </c>
@@ -22345,7 +22272,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="192" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>2013</v>
       </c>
@@ -22384,10 +22311,10 @@
         <v>8.9</v>
       </c>
       <c r="N192" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O192" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q192" s="1" t="s">
         <v>58</v>
@@ -22407,6 +22334,15 @@
       <c r="W192" s="1">
         <v>48.9</v>
       </c>
+      <c r="X192" s="1">
+        <v>572.79999999999995</v>
+      </c>
+      <c r="Y192" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="Z192" s="1">
+        <v>27.2</v>
+      </c>
       <c r="AE192" s="1">
         <v>0.30399999999999999</v>
       </c>
@@ -22435,7 +22371,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>2013</v>
       </c>
@@ -22474,10 +22410,10 @@
         <v>8.9</v>
       </c>
       <c r="N193" s="1">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="O193" s="1">
-        <v>516</v>
+        <v>1400</v>
       </c>
       <c r="Q193" s="1" t="s">
         <v>58</v>
@@ -22497,6 +22433,15 @@
       <c r="W193" s="1">
         <v>31.4</v>
       </c>
+      <c r="X193" s="1">
+        <v>538.5</v>
+      </c>
+      <c r="Y193" s="1">
+        <v>22</v>
+      </c>
+      <c r="Z193" s="1">
+        <v>24.8</v>
+      </c>
       <c r="AE193" s="1">
         <v>0.28599999999999998</v>
       </c>
@@ -22525,7 +22470,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="194" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>2013</v>
       </c>
@@ -22563,10 +22508,10 @@
         <v>8.9</v>
       </c>
       <c r="N194" s="1">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="O194" s="1">
-        <v>516</v>
+        <v>2204</v>
       </c>
       <c r="Q194" s="1" t="s">
         <v>58</v>
@@ -22614,7 +22559,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="195" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>2013</v>
       </c>
@@ -22653,10 +22598,10 @@
         <v>15.4</v>
       </c>
       <c r="N195" s="1">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="O195" s="1">
-        <v>516</v>
+        <v>2204</v>
       </c>
       <c r="Q195" s="1" t="s">
         <v>58</v>
@@ -22704,7 +22649,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="196" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>2013</v>
       </c>
@@ -22743,10 +22688,10 @@
         <v>8.9</v>
       </c>
       <c r="N196" s="1">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="O196" s="1">
-        <v>516</v>
+        <v>2204</v>
       </c>
       <c r="Q196" s="1" t="s">
         <v>58</v>
@@ -22794,7 +22739,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="197" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>2013</v>
       </c>
@@ -22833,10 +22778,10 @@
         <v>8.9</v>
       </c>
       <c r="N197" s="1">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="O197" s="1">
-        <v>516</v>
+        <v>2204</v>
       </c>
       <c r="Q197" s="1" t="s">
         <v>58</v>
@@ -22937,8 +22882,15 @@
       <c r="W198" s="1">
         <v>100</v>
       </c>
+      <c r="X198" s="1">
+        <v>443</v>
+      </c>
       <c r="Y198" s="1">
         <v>14.7</v>
+      </c>
+      <c r="Z198" s="1">
+        <f>X198/Y198</f>
+        <v>30.136054421768709</v>
       </c>
       <c r="AA198" s="1">
         <v>420.39673913043481</v>
@@ -23407,7 +23359,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="204" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>2021</v>
       </c>
@@ -23517,7 +23469,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="205" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>2021</v>
       </c>
@@ -23629,7 +23581,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="206" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>2021</v>
       </c>
@@ -23740,7 +23692,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="207" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>2021</v>
       </c>
@@ -23851,7 +23803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="208" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>2021</v>
       </c>
@@ -23962,7 +23914,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="209" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>2021</v>
       </c>
@@ -24073,7 +24025,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="210" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>2021</v>
       </c>
@@ -24187,7 +24139,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="211" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D211" s="1" t="s">
         <v>156</v>
       </c>
@@ -24292,7 +24244,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="212" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D212" s="1" t="s">
         <v>156</v>
       </c>
@@ -24397,7 +24349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="213" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D213" s="1" t="s">
         <v>156</v>
       </c>
@@ -24502,7 +24454,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="214" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D214" s="1" t="s">
         <v>156</v>
       </c>
@@ -24607,7 +24559,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="215" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D215" s="1" t="s">
         <v>156</v>
       </c>
@@ -24712,7 +24664,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="216" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D216" s="1" t="s">
         <v>156</v>
       </c>
@@ -24817,7 +24769,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="217" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D217" s="1" t="s">
         <v>156</v>
       </c>
@@ -24922,7 +24874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="218" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D218" s="1" t="s">
         <v>156</v>
       </c>
@@ -25027,7 +24979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="219" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D219" s="1" t="s">
         <v>156</v>
       </c>
@@ -25132,7 +25084,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="220" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D220" s="1" t="s">
         <v>156</v>
       </c>
@@ -25237,7 +25189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="221" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>2013</v>
       </c>
@@ -25349,7 +25301,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D222" s="1" t="s">
         <v>237</v>
       </c>
@@ -25452,7 +25404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="223" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D223" s="1" t="s">
         <v>237</v>
       </c>
@@ -25555,7 +25507,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="224" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D224" s="1" t="s">
         <v>237</v>
       </c>
@@ -25658,7 +25610,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="225" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D225" s="1" t="s">
         <v>237</v>
       </c>
@@ -25761,7 +25713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="226" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D226" s="1" t="s">
         <v>237</v>
       </c>
@@ -25864,7 +25816,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="227" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D227" s="1" t="s">
         <v>237</v>
       </c>
@@ -25967,7 +25919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="228" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D228" s="1" t="s">
         <v>237</v>
       </c>
@@ -26070,7 +26022,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="229" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D229" s="1" t="s">
         <v>237</v>
       </c>
@@ -26173,7 +26125,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="230" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D230" s="1" t="s">
         <v>237</v>
       </c>
@@ -26276,7 +26228,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="231" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D231" s="1" t="s">
         <v>237</v>
       </c>
@@ -26379,7 +26331,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="232" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D232" s="1" t="s">
         <v>237</v>
       </c>
@@ -26482,7 +26434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="233" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D233" s="1" t="s">
         <v>237</v>
       </c>
@@ -26585,7 +26537,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="234" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D234" s="1" t="s">
         <v>237</v>
       </c>
@@ -26688,7 +26640,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="235" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D235" s="1" t="s">
         <v>237</v>
       </c>
@@ -26791,7 +26743,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="236" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D236" s="1" t="s">
         <v>237</v>
       </c>
@@ -26894,7 +26846,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="237" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D237" s="1" t="s">
         <v>237</v>
       </c>
@@ -26997,7 +26949,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="238" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D238" s="1" t="s">
         <v>237</v>
       </c>
@@ -27100,7 +27052,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D239" s="1" t="s">
         <v>237</v>
       </c>
@@ -27203,7 +27155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="240" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D240" s="1" t="s">
         <v>237</v>
       </c>
@@ -27306,7 +27258,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="241" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D241" s="1" t="s">
         <v>237</v>
       </c>
@@ -27409,7 +27361,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="242" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D242" s="1" t="s">
         <v>237</v>
       </c>
@@ -27512,7 +27464,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="243" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D243" s="1" t="s">
         <v>237</v>
       </c>
@@ -27615,7 +27567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="244" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D244" s="1" t="s">
         <v>237</v>
       </c>
@@ -27718,7 +27670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="245" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D245" s="1" t="s">
         <v>237</v>
       </c>
@@ -27821,7 +27773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="246" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D246" s="1" t="s">
         <v>237</v>
       </c>
@@ -27924,7 +27876,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="247" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D247" s="1" t="s">
         <v>237</v>
       </c>
@@ -28027,7 +27979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="248" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D248" s="1" t="s">
         <v>237</v>
       </c>
@@ -28130,7 +28082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="249" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D249" s="1" t="s">
         <v>237</v>
       </c>
@@ -28233,7 +28185,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="250" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D250" s="1" t="s">
         <v>237</v>
       </c>
@@ -28336,7 +28288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="251" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D251" s="1" t="s">
         <v>237</v>
       </c>
@@ -28439,7 +28391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="252" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D252" s="1" t="s">
         <v>237</v>
       </c>
@@ -28542,7 +28494,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="253" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D253" s="1" t="s">
         <v>237</v>
       </c>
@@ -28645,7 +28597,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="254" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D254" s="1" t="s">
         <v>237</v>
       </c>
@@ -28748,7 +28700,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="255" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D255" s="1" t="s">
         <v>237</v>
       </c>
@@ -28851,7 +28803,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="256" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D256" s="1" t="s">
         <v>237</v>
       </c>
@@ -28954,7 +28906,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="257" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D257" s="1" t="s">
         <v>237</v>
       </c>
@@ -29057,7 +29009,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="258" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D258" s="1" t="s">
         <v>237</v>
       </c>
@@ -29160,7 +29112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="259" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D259" s="1" t="s">
         <v>237</v>
       </c>
@@ -29263,7 +29215,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="260" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D260" s="1" t="s">
         <v>237</v>
       </c>
@@ -29366,7 +29318,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="261" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D261" s="1" t="s">
         <v>237</v>
       </c>
@@ -29469,7 +29421,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="262" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D262" s="1" t="s">
         <v>237</v>
       </c>
@@ -29572,7 +29524,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="263" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D263" s="1" t="s">
         <v>237</v>
       </c>
@@ -29675,7 +29627,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="264" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D264" s="1" t="s">
         <v>237</v>
       </c>
@@ -29778,7 +29730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="265" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D265" s="1" t="s">
         <v>237</v>
       </c>
@@ -29881,7 +29833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="266" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D266" s="1" t="s">
         <v>237</v>
       </c>
@@ -29984,7 +29936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="267" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D267" s="1" t="s">
         <v>237</v>
       </c>
@@ -30087,7 +30039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="268" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D268" s="1" t="s">
         <v>237</v>
       </c>
@@ -30190,7 +30142,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="269" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D269" s="1" t="s">
         <v>237</v>
       </c>
@@ -30293,7 +30245,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="270" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D270" s="1" t="s">
         <v>237</v>
       </c>
@@ -30396,7 +30348,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="271" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D271" s="1" t="s">
         <v>237</v>
       </c>
@@ -30499,7 +30451,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="272" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D272" s="1" t="s">
         <v>237</v>
       </c>
@@ -30602,7 +30554,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="273" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D273" s="1" t="s">
         <v>237</v>
       </c>
@@ -30705,7 +30657,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="274" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D274" s="1" t="s">
         <v>237</v>
       </c>
@@ -30808,7 +30760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="275" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D275" s="1" t="s">
         <v>237</v>
       </c>
@@ -30911,7 +30863,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="276" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D276" s="1" t="s">
         <v>237</v>
       </c>
@@ -31014,7 +30966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="277" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D277" s="1" t="s">
         <v>237</v>
       </c>
@@ -31117,7 +31069,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="278" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D278" s="1" t="s">
         <v>237</v>
       </c>
@@ -31220,7 +31172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="279" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D279" s="1" t="s">
         <v>237</v>
       </c>
@@ -31323,7 +31275,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="280" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D280" s="1" t="s">
         <v>237</v>
       </c>
@@ -31426,7 +31378,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="281" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D281" s="1" t="s">
         <v>237</v>
       </c>
@@ -31529,7 +31481,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="282" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D282" s="1" t="s">
         <v>237</v>
       </c>
@@ -31632,7 +31584,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="283" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D283" s="1" t="s">
         <v>237</v>
       </c>
@@ -31735,7 +31687,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="284" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D284" s="1" t="s">
         <v>237</v>
       </c>
@@ -31838,7 +31790,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="285" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>2023</v>
       </c>
@@ -31943,7 +31895,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D286" s="1" t="s">
         <v>182</v>
       </c>
@@ -32039,7 +31991,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="287" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D287" s="1" t="s">
         <v>182</v>
       </c>
@@ -32135,7 +32087,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="288" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D288" s="1" t="s">
         <v>182</v>
       </c>
@@ -32231,7 +32183,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="289" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D289" s="1" t="s">
         <v>182</v>
       </c>
@@ -32327,7 +32279,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="290" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D290" s="1" t="s">
         <v>182</v>
       </c>
@@ -32423,7 +32375,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="291" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D291" s="1" t="s">
         <v>182</v>
       </c>
@@ -32519,7 +32471,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="292" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D292" s="1" t="s">
         <v>182</v>
       </c>
@@ -32615,7 +32567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="293" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D293" s="1" t="s">
         <v>182</v>
       </c>
@@ -32711,7 +32663,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="294" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D294" s="1" t="s">
         <v>182</v>
       </c>
@@ -32807,7 +32759,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="295" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D295" s="1" t="s">
         <v>182</v>
       </c>
@@ -32903,7 +32855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="296" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D296" s="1" t="s">
         <v>182</v>
       </c>
@@ -32999,7 +32951,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="297" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>2020</v>
       </c>
@@ -33107,7 +33059,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="298" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D298" s="1" t="s">
         <v>187</v>
       </c>
@@ -33197,7 +33149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="299" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D299" s="1" t="s">
         <v>187</v>
       </c>
@@ -33287,7 +33239,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="300" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D300" s="1" t="s">
         <v>187</v>
       </c>
@@ -33377,7 +33329,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="301" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D301" s="1" t="s">
         <v>187</v>
       </c>
@@ -33467,7 +33419,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="302" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D302" s="1" t="s">
         <v>187</v>
       </c>
@@ -33566,7 +33518,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="303" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D303" s="1" t="s">
         <v>187</v>
       </c>
@@ -33656,7 +33608,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="304" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D304" s="1" t="s">
         <v>187</v>
       </c>
@@ -33746,7 +33698,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="305" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D305" s="1" t="s">
         <v>187</v>
       </c>
@@ -33836,7 +33788,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="306" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D306" s="1" t="s">
         <v>187</v>
       </c>
@@ -33926,7 +33878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="307" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D307" s="1" t="s">
         <v>187</v>
       </c>
@@ -34022,7 +33974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="308" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D308" s="1" t="s">
         <v>187</v>
       </c>
@@ -34112,7 +34064,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="309" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D309" s="1" t="s">
         <v>187</v>
       </c>
@@ -34202,7 +34154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="310" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D310" s="1" t="s">
         <v>187</v>
       </c>
@@ -34292,7 +34244,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="311" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D311" s="1" t="s">
         <v>187</v>
       </c>
@@ -34382,7 +34334,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="312" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D312" s="1" t="s">
         <v>187</v>
       </c>
@@ -34478,7 +34430,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="313" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D313" s="1" t="s">
         <v>187</v>
       </c>
@@ -34568,7 +34520,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="314" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D314" s="1" t="s">
         <v>187</v>
       </c>
@@ -34658,7 +34610,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="315" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D315" s="1" t="s">
         <v>187</v>
       </c>
@@ -34748,7 +34700,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="316" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D316" s="1" t="s">
         <v>187</v>
       </c>
@@ -34838,7 +34790,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="317" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D317" s="1" t="s">
         <v>187</v>
       </c>
@@ -34934,7 +34886,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="318" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D318" s="1" t="s">
         <v>187</v>
       </c>
@@ -35024,7 +34976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="319" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D319" s="1" t="s">
         <v>187</v>
       </c>
@@ -35114,7 +35066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="320" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D320" s="1" t="s">
         <v>187</v>
       </c>
@@ -35204,7 +35156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="321" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D321" s="1" t="s">
         <v>187</v>
       </c>
@@ -35294,7 +35246,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="322" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D322" s="1" t="s">
         <v>187</v>
       </c>
@@ -35390,7 +35342,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="323" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D323" s="1" t="s">
         <v>187</v>
       </c>
@@ -35480,7 +35432,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="324" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D324" s="1" t="s">
         <v>187</v>
       </c>
@@ -35570,7 +35522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="325" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D325" s="1" t="s">
         <v>187</v>
       </c>
@@ -35660,7 +35612,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="326" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D326" s="1" t="s">
         <v>187</v>
       </c>
@@ -35750,7 +35702,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="327" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>2016</v>
       </c>
@@ -35870,7 +35822,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="328" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D328" s="1" t="s">
         <v>190</v>
       </c>
@@ -35939,7 +35891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D329" s="1" t="s">
         <v>190</v>
       </c>
@@ -36050,7 +36002,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="330" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D330" s="1" t="s">
         <v>190</v>
       </c>
@@ -36161,7 +36113,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="331" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D331" s="1" t="s">
         <v>190</v>
       </c>
@@ -36272,7 +36224,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="332" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D332" s="1" t="s">
         <v>190</v>
       </c>
@@ -36383,7 +36335,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="333" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D333" s="1" t="s">
         <v>190</v>
       </c>
@@ -36494,7 +36446,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D334" s="1" t="s">
         <v>190</v>
       </c>
@@ -36563,7 +36515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D335" s="1" t="s">
         <v>190</v>
       </c>
@@ -36674,7 +36626,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="336" spans="1:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D336" s="1" t="s">
         <v>190</v>
       </c>
@@ -36785,7 +36737,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="337" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D337" s="1" t="s">
         <v>190</v>
       </c>
@@ -36896,7 +36848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="338" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D338" s="1" t="s">
         <v>190</v>
       </c>
@@ -37007,7 +36959,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="339" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A339" s="5">
         <v>2013</v>
       </c>
@@ -37141,7 +37093,7 @@
       <c r="BY339" s="9"/>
       <c r="BZ339" s="9"/>
     </row>
-    <row r="340" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A340" s="5"/>
       <c r="B340" s="6"/>
       <c r="C340" s="6"/>
@@ -37271,7 +37223,7 @@
       <c r="BY340" s="9"/>
       <c r="BZ340" s="9"/>
     </row>
-    <row r="341" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A341" s="5"/>
       <c r="B341" s="6"/>
       <c r="C341" s="6"/>
@@ -37401,7 +37353,7 @@
       <c r="BY341" s="9"/>
       <c r="BZ341" s="9"/>
     </row>
-    <row r="342" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A342" s="5"/>
       <c r="B342" s="6"/>
       <c r="C342" s="6"/>
@@ -37531,7 +37483,7 @@
       <c r="BY342" s="9"/>
       <c r="BZ342" s="9"/>
     </row>
-    <row r="343" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A343" s="5"/>
       <c r="B343" s="6"/>
       <c r="C343" s="6"/>
@@ -37661,7 +37613,7 @@
       <c r="BY343" s="9"/>
       <c r="BZ343" s="9"/>
     </row>
-    <row r="344" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A344" s="5"/>
       <c r="B344" s="6"/>
       <c r="C344" s="6"/>
@@ -37790,7 +37742,7 @@
       <c r="BY344" s="9"/>
       <c r="BZ344" s="9"/>
     </row>
-    <row r="345" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A345" s="5"/>
       <c r="B345" s="6"/>
       <c r="C345" s="6"/>
@@ -37920,7 +37872,7 @@
       <c r="BY345" s="9"/>
       <c r="BZ345" s="9"/>
     </row>
-    <row r="346" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A346" s="5"/>
       <c r="B346" s="6"/>
       <c r="C346" s="6"/>
@@ -38050,7 +38002,7 @@
       <c r="BY346" s="9"/>
       <c r="BZ346" s="9"/>
     </row>
-    <row r="347" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A347" s="5"/>
       <c r="B347" s="6"/>
       <c r="C347" s="6"/>
@@ -38180,7 +38132,7 @@
       <c r="BY347" s="9"/>
       <c r="BZ347" s="9"/>
     </row>
-    <row r="348" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A348" s="5"/>
       <c r="B348" s="6"/>
       <c r="C348" s="6"/>
@@ -38310,7 +38262,7 @@
       <c r="BY348" s="9"/>
       <c r="BZ348" s="9"/>
     </row>
-    <row r="349" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A349" s="5"/>
       <c r="B349" s="6"/>
       <c r="C349" s="6"/>
@@ -38439,7 +38391,7 @@
       <c r="BY349" s="9"/>
       <c r="BZ349" s="9"/>
     </row>
-    <row r="350" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A350" s="5"/>
       <c r="B350" s="6"/>
       <c r="C350" s="6"/>
@@ -38569,7 +38521,7 @@
       <c r="BY350" s="9"/>
       <c r="BZ350" s="9"/>
     </row>
-    <row r="351" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A351" s="5"/>
       <c r="B351" s="6"/>
       <c r="C351" s="6"/>
@@ -38699,7 +38651,7 @@
       <c r="BY351" s="9"/>
       <c r="BZ351" s="9"/>
     </row>
-    <row r="352" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A352" s="5"/>
       <c r="B352" s="6"/>
       <c r="C352" s="6"/>
@@ -38829,7 +38781,7 @@
       <c r="BY352" s="9"/>
       <c r="BZ352" s="9"/>
     </row>
-    <row r="353" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A353" s="5"/>
       <c r="B353" s="6"/>
       <c r="C353" s="6"/>
@@ -38959,7 +38911,7 @@
       <c r="BY353" s="9"/>
       <c r="BZ353" s="9"/>
     </row>
-    <row r="354" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A354" s="5"/>
       <c r="B354" s="6"/>
       <c r="C354" s="6"/>
@@ -39088,7 +39040,7 @@
       <c r="BY354" s="9"/>
       <c r="BZ354" s="9"/>
     </row>
-    <row r="355" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A355" s="5"/>
       <c r="B355" s="6"/>
       <c r="C355" s="6"/>
@@ -39218,7 +39170,7 @@
       <c r="BY355" s="9"/>
       <c r="BZ355" s="9"/>
     </row>
-    <row r="356" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A356" s="5"/>
       <c r="B356" s="6"/>
       <c r="C356" s="6"/>
@@ -39348,7 +39300,7 @@
       <c r="BY356" s="9"/>
       <c r="BZ356" s="9"/>
     </row>
-    <row r="357" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A357" s="5"/>
       <c r="B357" s="6"/>
       <c r="C357" s="6"/>
@@ -39478,7 +39430,7 @@
       <c r="BY357" s="9"/>
       <c r="BZ357" s="9"/>
     </row>
-    <row r="358" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A358" s="5"/>
       <c r="B358" s="6"/>
       <c r="C358" s="6"/>
@@ -39608,7 +39560,7 @@
       <c r="BY358" s="9"/>
       <c r="BZ358" s="9"/>
     </row>
-    <row r="359" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A359" s="5"/>
       <c r="B359" s="6"/>
       <c r="C359" s="6"/>
@@ -39737,7 +39689,7 @@
       <c r="BY359" s="9"/>
       <c r="BZ359" s="9"/>
     </row>
-    <row r="360" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A360" s="5"/>
       <c r="B360" s="6"/>
       <c r="C360" s="6"/>
@@ -39867,7 +39819,7 @@
       <c r="BY360" s="9"/>
       <c r="BZ360" s="9"/>
     </row>
-    <row r="361" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A361" s="5"/>
       <c r="B361" s="6"/>
       <c r="C361" s="6"/>
@@ -39997,7 +39949,7 @@
       <c r="BY361" s="9"/>
       <c r="BZ361" s="9"/>
     </row>
-    <row r="362" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A362" s="5"/>
       <c r="B362" s="6"/>
       <c r="C362" s="6"/>
@@ -40127,7 +40079,7 @@
       <c r="BY362" s="9"/>
       <c r="BZ362" s="9"/>
     </row>
-    <row r="363" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A363" s="5"/>
       <c r="B363" s="6"/>
       <c r="C363" s="6"/>
@@ -40257,7 +40209,7 @@
       <c r="BY363" s="9"/>
       <c r="BZ363" s="9"/>
     </row>
-    <row r="364" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A364" s="5"/>
       <c r="B364" s="6"/>
       <c r="C364" s="6"/>
@@ -40386,7 +40338,7 @@
       <c r="BY364" s="9"/>
       <c r="BZ364" s="9"/>
     </row>
-    <row r="365" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A365" s="5"/>
       <c r="B365" s="6"/>
       <c r="C365" s="6"/>
@@ -40516,7 +40468,7 @@
       <c r="BY365" s="9"/>
       <c r="BZ365" s="9"/>
     </row>
-    <row r="366" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A366" s="5"/>
       <c r="B366" s="6"/>
       <c r="C366" s="6"/>
@@ -40646,7 +40598,7 @@
       <c r="BY366" s="9"/>
       <c r="BZ366" s="9"/>
     </row>
-    <row r="367" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A367" s="5"/>
       <c r="B367" s="6"/>
       <c r="C367" s="6"/>
@@ -40776,7 +40728,7 @@
       <c r="BY367" s="9"/>
       <c r="BZ367" s="9"/>
     </row>
-    <row r="368" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A368" s="5"/>
       <c r="B368" s="6"/>
       <c r="C368" s="6"/>
@@ -40906,7 +40858,7 @@
       <c r="BY368" s="9"/>
       <c r="BZ368" s="9"/>
     </row>
-    <row r="369" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A369" s="5"/>
       <c r="B369" s="6"/>
       <c r="C369" s="6"/>
@@ -41035,7 +40987,7 @@
       <c r="BY369" s="9"/>
       <c r="BZ369" s="9"/>
     </row>
-    <row r="370" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A370" s="5"/>
       <c r="B370" s="6"/>
       <c r="C370" s="6"/>
@@ -41165,7 +41117,7 @@
       <c r="BY370" s="9"/>
       <c r="BZ370" s="9"/>
     </row>
-    <row r="371" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A371" s="5"/>
       <c r="B371" s="6"/>
       <c r="C371" s="6"/>
@@ -41295,7 +41247,7 @@
       <c r="BY371" s="9"/>
       <c r="BZ371" s="9"/>
     </row>
-    <row r="372" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A372" s="5"/>
       <c r="B372" s="6"/>
       <c r="C372" s="6"/>
@@ -41425,7 +41377,7 @@
       <c r="BY372" s="9"/>
       <c r="BZ372" s="9"/>
     </row>
-    <row r="373" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A373" s="5"/>
       <c r="B373" s="6"/>
       <c r="C373" s="6"/>
@@ -41555,7 +41507,7 @@
       <c r="BY373" s="9"/>
       <c r="BZ373" s="9"/>
     </row>
-    <row r="374" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A374" s="5"/>
       <c r="B374" s="6"/>
       <c r="C374" s="6"/>
@@ -41684,7 +41636,7 @@
       <c r="BY374" s="9"/>
       <c r="BZ374" s="9"/>
     </row>
-    <row r="375" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A375" s="5"/>
       <c r="B375" s="6"/>
       <c r="C375" s="6"/>
@@ -41814,7 +41766,7 @@
       <c r="BY375" s="9"/>
       <c r="BZ375" s="9"/>
     </row>
-    <row r="376" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A376" s="5"/>
       <c r="B376" s="6"/>
       <c r="C376" s="6"/>
@@ -41944,7 +41896,7 @@
       <c r="BY376" s="9"/>
       <c r="BZ376" s="9"/>
     </row>
-    <row r="377" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A377" s="5"/>
       <c r="B377" s="6"/>
       <c r="C377" s="6"/>
@@ -42074,7 +42026,7 @@
       <c r="BY377" s="9"/>
       <c r="BZ377" s="9"/>
     </row>
-    <row r="378" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A378" s="5"/>
       <c r="B378" s="6"/>
       <c r="C378" s="6"/>
@@ -42204,7 +42156,7 @@
       <c r="BY378" s="9"/>
       <c r="BZ378" s="9"/>
     </row>
-    <row r="379" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>2019</v>
       </c>
@@ -42323,7 +42275,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="380" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D380" s="1" t="s">
         <v>213</v>
       </c>
@@ -42434,7 +42386,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="381" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D381" s="1" t="s">
         <v>213</v>
       </c>
@@ -42545,7 +42497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="382" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D382" s="1" t="s">
         <v>213</v>
       </c>
@@ -42656,7 +42608,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="383" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D383" s="1" t="s">
         <v>213</v>
       </c>
@@ -42767,7 +42719,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="384" spans="1:78" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:78" x14ac:dyDescent="0.25">
       <c r="D384" s="1" t="s">
         <v>213</v>
       </c>
@@ -42878,7 +42830,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="385" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D385" s="1" t="s">
         <v>213</v>
       </c>
@@ -42988,7 +42940,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="386" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D386" s="1" t="s">
         <v>213</v>
       </c>
@@ -43099,7 +43051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="387" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D387" s="1" t="s">
         <v>213</v>
       </c>
@@ -43210,7 +43162,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="388" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D388" s="1" t="s">
         <v>213</v>
       </c>
@@ -43321,7 +43273,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="389" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D389" s="1" t="s">
         <v>213</v>
       </c>
@@ -43432,7 +43384,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="390" spans="4:45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:45" x14ac:dyDescent="0.25">
       <c r="D390" s="1" t="s">
         <v>213</v>
       </c>
@@ -43544,13 +43496,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS390" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="McKee et al., 2016"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="AE71:AK86">
     <cfRule type="colorScale" priority="1">
